--- a/Excel-Finance/Finance-And-Accounting-01/VLookUp.xlsx
+++ b/Excel-Finance/Finance-And-Accounting-01/VLookUp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\books-and-tutorials\Finance-Excel\Part 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel-Finance\Finance-And-Accounting-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7300D15-1E36-4AE6-88F3-A01AA3032056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE28A6B-D0E6-4107-A867-BEDE5BFDF106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -298,7 +298,7 @@
   <numFmts count="3">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -423,7 +423,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -644,14 +644,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
-    <col min="13" max="13" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" customWidth="1"/>
+    <col min="13" max="13" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -691,7 +692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>7</v>
       </c>
@@ -732,7 +733,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="9">
         <v>8</v>
       </c>
@@ -768,7 +769,7 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>12</v>
       </c>
@@ -804,7 +805,7 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -840,7 +841,7 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>13</v>
       </c>
@@ -876,7 +877,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>14</v>
       </c>
@@ -912,7 +913,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>17</v>
       </c>
@@ -948,7 +949,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>16</v>
       </c>
@@ -984,7 +985,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2</v>
       </c>
@@ -1020,7 +1021,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -1056,7 +1057,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>22</v>
       </c>
@@ -1092,7 +1093,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>6</v>
       </c>
@@ -1128,7 +1129,7 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>20</v>
       </c>
@@ -1164,7 +1165,7 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>9</v>
       </c>
@@ -1200,7 +1201,7 @@
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>21</v>
       </c>
@@ -1236,7 +1237,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>19</v>
       </c>
@@ -1272,7 +1273,7 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>1</v>
       </c>
@@ -1308,7 +1309,7 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
     </row>
-    <row r="19" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>10</v>
       </c>
@@ -1344,7 +1345,7 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
     </row>
-    <row r="20" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>3</v>
       </c>
@@ -1380,7 +1381,7 @@
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
     </row>
-    <row r="21" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>15</v>
       </c>
@@ -1416,7 +1417,7 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
     </row>
-    <row r="22" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>18</v>
       </c>
@@ -1452,7 +1453,7 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
     </row>
-    <row r="23" spans="1:14" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>4</v>
       </c>
@@ -1488,7 +1489,7 @@
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
     </row>
-    <row r="24" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
